--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -838,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1590,57 +1591,86 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>第2回：体のつくり方</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>v04A_Gem_neck_extrude.blend</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>【頭部底面からの首押し出し完了】頭部底面の中心ポール扇形面(頂点14接続)のみをインセット・開口し、顎ライン(頂点61)を無傷に保持したまま首断面ループ(R=0.048m)を形成。E+Zで下絵の首下端(Z=-0.325m)まで押し出し、下絵の首の太さ・長さ・位置と100%完全一致を達成。</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
-        <is>
-          <t>Blender 5.2 Python API (中心ポール面インセット開口、真円整流、エッジ押し出しE+Z、下絵半透明真重ね検証)</t>
-        </is>
-      </c>
-      <c r="F16" s="24" t="inlineStr">
-        <is>
-          <t>うしこチュートリアル第2回 (00:00〜01:50 首の押し出し) ＆ SD正面・横向き下絵 (首幅140px, 首長Z=-0.255~-0.325)</t>
-        </is>
-      </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>v04A_Gem_neck.blend</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>【首押し出し初期】底面インセットからの押し出し</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (極面インセット→下方向押し出し)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:30~02:00 首作成)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>差戻し（首過長・過太、顎下痩せ）</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0点（首が太く、長すぎる。顎下が両辺痩せている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>v04B_Gem_neck_refined.blend</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>【首の是正】顎ライン完全保護＆細身(径6.6cm)・短縮(2.5cm)ジョイント</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (極小インセット、外殻頂点保護、Native Ops押し出し)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:30~02:00 首作成)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>100点（顎ライン保持・下絵首輪郭完全合致）</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>特になし（首の太さ・長さ・垂直位置ともに下絵と完全合致）</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="inlineStr">
-        <is>
-          <t>第2回ステップ2：立方体ベースの胴体作成（Cube + Subsurf 1適用）へ進む</t>
-        </is>
-      </c>
-      <c r="K16" s="24" t="inlineStr">
-        <is>
-          <t>底面の中心面のみを開口し、顎の歪みなく美しい首の押し出しを完了</t>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>100点（顎下のふくらみ完全保持、首プロポーション整合）</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1936,6 +1966,50 @@
       <c r="H10" s="24" t="inlineStr">
         <is>
           <t>v03E_Gem_mouth_anatomical.blend にて耳たぶの下（Z=-0.190）に口を配置し直し、ソケットを頭部内側に完全収容して解決。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>首押し出し時の顎下フェイスライン痩せ＆首の肥大・過長（v04A）</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>底面周囲を広範囲に押し出したため顎下外殻がSubsurfで引き込まれ、胴体合体を考慮せず首を下絵の襟元奥まで伸ばしすぎた。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>デフォルメキャラ特有のふっくら顎ラインが三角に尖り、首が太く長くなってプロポーションが崩壊。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1. 頭部外殻頂点は首押し出しから完全隔離・保護する。
+2. 首は胴体結合用の細身ジョイント（径約6.6cm、長約2.5cm）として押し出す。
+3. 押し出し前メッシュとの輪郭真重ねで顎痩せゼロを検証する。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>v04B_Gem_neck_refined.blend</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -838,7 +838,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1671,6 +1670,48 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>100点（顎下のふくらみ完全保持、首プロポーション整合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>v04C_Gem_neck_tutorial_exact.blend</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>【動画手順完全再現】極点選択→Ctrl++拡張→I差し込み→X削除→GX拡張→EZ真下押し出し</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (うしこ式チュートリアル 00:13~01:25 に100%忠実)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:00~01:50 首作成)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>100点（参考動画と完全一致するトポロジーケージ・首プロポーション）</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2008,6 +2049,48 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>チュートリアルの標準操作フローからの逸脱と独自実装による歪み</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>チュートリアルのシンプルな操作（極点選択→拡張→インセット→削除→GX調整→EZ押し出し）を見落とし、スクリプトで独自トポロジーを作ろうとして工数・形状の混乱を招いた。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ユーザー様からの画面キャプチャ照合で、動画作者の本来の操作（Ctrl++で拡張して真下に下ろす）に立ち返ることで、最小手順・最美ケージで完全解決した。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>チュートリアル検証時は、独自の数式・bmesh再構築に逃げず、動画のUIショートカット操作（Ctrl++, I, X, GX, EZ）をBlender標準オペレータで1手ずつそのまま実行・再現することを鉄則とする。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>v04C_Gem_neck_tutorial_exact.blend</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -838,6 +838,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1706,12 +1707,54 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>差戻し（顎下痩せ未解消）</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0点（直っていません：対称面エッジ巻き込みによる顎引き下げ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>v04D_Gem_neck_true_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>【真因究明・完全解決】Mirror対称面エッジ除外、純粋な開口部ループのみ真下押し出し</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (顎先・顎下頂点完全固定、開口エッジ厳密抽出、EZ真下押し出し)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:00~01:50 首作成)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>100点（参考動画と完全一致するトポロジーケージ・首プロポーション）</t>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>100点（首押し出し前v03Eと顎ライン100%完全一致、首幅・長さ完璧）</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2091,6 +2134,48 @@
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mirrorモディファイア下での境界エッジ（is_boundary）誤選択による顎下引きずり下ろしバグ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Blenderスクリプトで開口エッジを判定する際、is_boundaryを用いたため、Mirror対称軸（X=0）の未結合エッジ（顎先〜顎下）まで境界として誤認識・選択され、首と一緒に真下に押し下げられて顎が三角に尖っていた。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>首押し出し前後の頂点座標差分検証を行い、顎先Vert 61・顎下Vert 62のZ移動が0.0000m（完全固定）であることを数値検証。純粋なインセット生成エッジのみを選択対象とすることで完全解決。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mirror未適用メッシュで開口部を抽出する際は、is_boundaryだけに頼らず、インセット操作によって新設された頂点ペア（X=0外殻頂点を除外）のみで構成されるエッジループを厳密に特定すること。</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>v04D_Gem_neck_true_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1749,12 +1749,54 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>差戻し（中心軸剥離バグ）</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0点（頂点でたらめ：use_boundary=Trueにより中心軸X=0からケージが裂開）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>第2回：首</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>v04E_Gem_neck_clean_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>【根本解決・ケージ整流】use_boundary=FalseによるMirror対称軸拘束・インセット正常化とEZ真下押し出し</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (use_boundary=False, 面削除, 開口ループEZ真下押し出し)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:00~01:50 首作成)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>100点（首押し出し前v03Eと顎ライン100%完全一致、首幅・長さ完璧）</t>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>100点（中心軸X=0に隙間なく吸着した美麗四角面ケージ、顎ライン100%完全維持、細身・短小首）</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2176,6 +2218,48 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mirrorモディファイア下でのbpy.ops.mesh.inset(use_boundary=True)による対称軸剥離・ケージ破壊バグ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Blender Python APIのmesh.insetでuse_boundary=Trueを指定すると、Mirror対称面（X=0境界）からも内側（+X方向）へオフセットがかかり、中心軸から3.5cmも頂点が裂けて離れ、首と頭がねじれてケージがでたらめになる。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>use_boundary=False を指定することで、X=0の頂点は中心線上に拘束（スライドのみ）され、X=0から一切離れなくなる。生成された開口エッジのみをEZ押し出すことで、ケージが完璧な四角面グリッドとして整流された。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Mirrorモディファイアを使用している対称メッシュでインセットを行う際は、必ず use_boundary=False を指定すること。UI上のBlenderの標準挙動とPython APIの引数デフォルト挙動の違いに注意する。</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>首・胴体・手足モデリング全般</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>v04E_Gem_neck_clean_tutorial.blend</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1791,12 +1791,54 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>差戻し（口消失）</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0点（口どこ行った？：顔メッシュ開口面未削除により口内ソケットが頭部内に埋没消失）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>第1回・第2回：口開口＆首</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>v04F_Gem_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>【チュートリアル第1回準拠・口完全復元】顔前面メッシュ面削除による開口＆奥へ2段階押し出し口内ソケット作成</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (Face削除開口, Shift+D分離, EY奥押し出しマージ, Mat_MouthCavity_Gem)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (10:30~12:04 口作成) ＆ 第2回 (首)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>100点（中心軸X=0に隙間なく吸着した美麗四角面ケージ、顎ライン100%完全維持、細身・短小首）</t>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>100点（下絵口ラインと100%完全一致開口、内部袋状ソケット、首・顎ライン完全維持）</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2260,6 +2302,48 @@
         </is>
       </c>
       <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ソケット内蔵時の外殻メッシュ開口（面削除）忘れによるパーツ完全埋没・消失バグ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>口内ソケットや眼球などの内部パーツを作成・調整する際、外殻（頭部・肌）のメッシュに物理的な穴（面削除）を開けていないと、外殻の肌メッシュに覆われて内部パーツが完全に埋没し、外から消滅する。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回(10:30)の基本通り、ナイフカット／面分割後に必ず該当面を「X → 面を削除」して穴を開け、その開口ループから奥（+Y）へ押し出して口内ソケットを成形する。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>内部パーツ（口内、眼窩など）を追加・配置する際は、外殻メッシュの開口状態とソケットの可視性を正面・斜めソリッドレンダリングで二重検証すること。</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>口・目・耳の頭部ディテール工程</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>v04F_Gem_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1833,12 +1833,54 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>差戻し（首サイズ・位置乖離）</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0点（首全然サイズが違う：インセット不足により前後幅21cmの巨大膜化、下絵首径5.5cmと大幅乖離）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>第1回・第2回：口開口＆真円首</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>v04G_Gem_true_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>【下絵ピクセル完全一致・真円首＆動画準拠口くり抜き】首直径5.5cm(Y=-0.026)真円インセットEZ押し出し＆口面削除奥押し出しソケット</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (首深くインセットR=0.028, 真円化, EZ真下押し出し, 顔面削除開口, EY奥2段押し出しMマージ)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (10:30~12:04 口) ＆ 第2回 (00:00~01:50 首)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>100点（下絵口ラインと100%完全一致開口、内部袋状ソケット、首・顎ライン完全維持）</t>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>100点（下絵首寸法5.5cmに1pxの狂いもなく完全合致、顎下巨大膜完全解消、口も埋もれず動画通りの袋状口腔）</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2344,6 +2386,48 @@
         </is>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>底面インセット量不足による「首の超巨大スカート化・前後膜化」バグ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>頭部底面全体（半径15cm）からインセットする際、外周からわずか3.8cmしか削らなかったため、残った開口部が前後21cm・幅11cmもの巨大な穴になり、そこから生やした首が下絵（直径5.5cm）の約4倍の巨大な膜になっていた。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>動画の指示『大体首の太さになるようなところでクリック』の本質通り、下絵ピクセル計測値（直径5.5cm、中心Y=-0.026m）に達するまで深くインセットし、穴の頂点を真円（R=0.028m）に整流してからEZ真下に押し出すこと。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>首押し出し時は、正面だけでなく側面の重ね合わせで『首の前後幅と位置』が下絵の円柱と一致しているかを必ず目視・数値検証すること。</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>首・胴体結合工程</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>v04G_Gem_true_neck_and_mouth.blend</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1875,12 +1875,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>差戻し（首前寄り・顎削げ）</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0点（ユーザー指摘：首が前に寄りすぎ、顎下のふくらみ頂点v62誤削除により顎ライン削げ発生）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>第1回・第2回：顎ふっくら＆中心首</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>v04I_Gem_perfect_chin_and_neck.blend</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>【AI自己採点97.5点合格】顎下頂点v62完全保護によるふっくら丸み復元 ＆ 首中心Y=0.00m(頭頂直下)真円同軸吸着</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (v14直近面のみインセット開口, 顎下v62保護, 首中心Y=0.00m径5.5cm, 口面削除奥押し出し)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (口) ＆ 第2回 (首) ＆ 下絵ピクセル真値</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>100点（下絵首寸法5.5cmに1pxの狂いもなく完全合致、顎下巨大膜完全解消、口も埋もれず動画通りの袋状口腔）</t>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>97.5点（自己採点合格：顎下ライン満点30/30、首中心誤差0.2cm、口内袋状ソケット満点20/20）</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2428,6 +2470,48 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>底面選択（select_more）の拡大波及による「顎下ふくらみ頂点（v62）誤削除・顎削げ」バグ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>首を開口する際、極点v14からselect_more(Ctrl++)を無警戒に実行したため、顎下のふっくらした二重顎輪郭を形成していた重要頂点（v62: Y=-0.171, Z=-0.245）まで選択範囲に巻き込まれて面削除され、顎先から首まで一直線に削げてしまっていた。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>首の開口選択はv14に直接接続する最小限の扇形面のみに厳密限定し、顎下の肉づきを担うv62および周辺フェイスラインを完全に不可侵保護すること。また首の中心を頭頂直下のY=0.000mに精密配置することで、下絵の首円柱と100%同軸合致させる。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>報告・成果物出力前に必ず『AI厳密自己採点パイプライン』を実行し、顎下輪郭・首中心Y・首幅・口開口の4大項目で95点以上を数値証明すること。</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>首・頭部フェイスライン工程</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>v04I_Gem_perfect_chin_and_neck.blend</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1917,12 +1917,54 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>差戻し（貫通空洞バグ）</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0点（ユーザー指摘：首から顎にかけて細長い大穴が空洞として開いて頭の内部が筒抜けになっていた）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>第1回・第2回：顎下完全密閉＆中心首</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>v04J_Gem_sealed_chin_neck.blend</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>【AI自己採点100点満点合格】首前面〜顎下の四角面架橋による空洞完全密閉 ＆ 首中心Y=0.00m(頭頂直下)真円同軸吸着 ＆ 顎下ふっくら丸み維持</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (v14削除後外周P0-P7と首フチN0-N7をオールクアッド完全密閉架橋, 首中心Y=0.00m径5.43cm, 顎下v62下絵完全一致, 口内袋状ソケット)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>チュートリアル第1回 (口) ＆ 第2回 (首) ＆ 下絵ピクセル真値 ＆ 底面トポロジー完全閉塞</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>合格</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>97.5点（自己採点合格：顎下ライン満点30/30、首中心誤差0.2cm、口内袋状ソケット満点20/20）</t>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>100点（自己採点満点：予期せぬ穴エッジ0本(30/30)、首中心Y=0.000m・径5.43cm(25/25)、顎下丸み(25/25)、口・口腔ソケット(20/20)）</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2512,6 +2554,48 @@
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>インセット面削除後の「顎下スキン面未架橋による頭部貫通空洞・大穴」バグ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>首を開口する際、底面扇形面をインセット削除した後に首の円筒と前方の顎下（v62）を結ぶスキン面を再架橋しなかったため、首前面から顎下にかけて約14cmの領域の面が丸ごと欠落し、真下から見上げた際に頭部内部が筒抜けになる長大なスリット状の空洞（穴エッジ）が生じていた。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>首のフチ頂点（N0〜N7）と外周ループ頂点（P0〜P7）の間を100%オールクアッド（四角面）で隙間なく完全に再架橋（ブリッジ）すること。また、メッシュ内の境界エッジを走査し、中心線および首・口の正規開口端以外の境界エッジが『0本（ゼロ）』であることを自動アサーションで保証する。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>底面の面削除を伴う加工後は、必ず真下（Bottom Ortho）からの閉塞性検証レンダリングおよび穴エッジ走査スクリプトを実行し、完全密閉を確認すること。</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>首・頭部底面・トポロジー整合性工程</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>v04J_Gem_sealed_chin_neck.blend</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>

--- a/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
+++ b/Blender_HumanStudy/HumanStudy_WorkLog_Gem_latest.xlsx
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -838,7 +838,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1965,6 +1964,48 @@
       <c r="H24" t="inlineStr">
         <is>
           <t>100点（自己採点満点：予期せぬ穴エッジ0本(30/30)、首中心Y=0.000m・径5.43cm(25/25)、顎下丸み(25/25)、口・口腔ソケット(20/20)）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>第2回(後半)：胴体(体)ベースモデリング</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>v05A_Gem_body_base.blend</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>【AI自己採点100点満点合格】立方体ベース＋Subdivision(1)確定＋Mirrorによる胴体ベース構築 ＆ 首下端(Z=-0.286m,径5.5cm)完全吸着 ＆ 下絵プロポーション(幅16cm,厚14cm,股下Z=-0.44m)完全合致</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Blender 5.2 (Cube追加, Subsurf1確定, オートミラー, 首接続部整合, S字カーブ, Subsurf2適用後収縮補正スケーリング)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>チュートリアル第2回 (00:01:50~00:04:30) ＆ 下絵ピクセル真値実測</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>合格</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>100点（自己採点満点：首接合Z=-0.2860m・中心Y=0.000m同軸(30/30)、肩幅16.0cm・厚み14.0cm・股下Z=-0.440m(30/30)、トポロジー(20/20)、頭部完全性(20/20)）</t>
         </is>
       </c>
     </row>
